--- a/data/cepea-consulta-soja-paranagua.reparado.xlsx
+++ b/data/cepea-consulta-soja-paranagua.reparado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\painel-controle-commodities\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1609F109-F47F-45B0-9D3A-1A0911B2DEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C560AA-A70D-4087-B0CC-25392F172A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-soja-paranagua.reparado.xlsx
+++ b/data/cepea-consulta-soja-paranagua.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A63044D-28EA-49EE-9EE1-091368ADAF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{009B2B35-EC7E-4C1B-83DF-58D4887AA224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="1070">
   <si>
     <t>Soja | INDICADOR DA SOJA CEPEA/ESALQ - PARANAGUÁ</t>
   </si>
@@ -3221,6 +3221,27 @@
   </si>
   <si>
     <t>141,89</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>140,54</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>139,65</t>
+  </si>
+  <si>
+    <t>25,70</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>140,26</t>
   </si>
 </sst>
 </file>
@@ -3672,7 +3693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J419"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8267,6 +8288,39 @@
       </c>
       <c r="C416" s="3" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-soja-paranagua.reparado.xlsx
+++ b/data/cepea-consulta-soja-paranagua.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{009B2B35-EC7E-4C1B-83DF-58D4887AA224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A0C51B9-D4FB-49E4-8295-6F08E31AA5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1072">
   <si>
     <t>Soja | INDICADOR DA SOJA CEPEA/ESALQ - PARANAGUÁ</t>
   </si>
@@ -3242,6 +3242,12 @@
   </si>
   <si>
     <t>140,26</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>139,66</t>
   </si>
 </sst>
 </file>
@@ -3693,7 +3699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J419"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8321,6 +8327,17 @@
       </c>
       <c r="C419" s="3" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>
